--- a/research/traditional_assets/database/data/british_virgin_islands/british_virgin_islands_metals_mining.xlsx
+++ b/research/traditional_assets/database/data/british_virgin_islands/british_virgin_islands_metals_mining.xlsx
@@ -587,26 +587,8 @@
           <t>Metals &amp; Mining</t>
         </is>
       </c>
-      <c r="D2">
-        <v>0.38</v>
-      </c>
-      <c r="G2">
-        <v>-1595.714285714286</v>
-      </c>
-      <c r="H2">
-        <v>-1595.714285714286</v>
-      </c>
-      <c r="I2">
-        <v>-2133.142857142857</v>
-      </c>
-      <c r="J2">
-        <v>-2133.142857142857</v>
-      </c>
       <c r="K2">
-        <v>-26.86</v>
-      </c>
-      <c r="L2">
-        <v>-3837.142857142857</v>
+        <v>-20.25</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +612,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>38.67</v>
+        <v>9.744</v>
       </c>
       <c r="V2">
-        <v>0.06578880212320727</v>
+        <v>0.02370226222330333</v>
       </c>
       <c r="W2">
-        <v>-0.1490909090909091</v>
+        <v>-0.1713995943204868</v>
       </c>
       <c r="X2">
-        <v>0.2291932889103916</v>
+        <v>0.1275361145052037</v>
       </c>
       <c r="Y2">
-        <v>-0.3782841980013007</v>
+        <v>-0.2989357088256905</v>
       </c>
       <c r="Z2">
-        <v>4.342620337111413e-05</v>
+        <v>0</v>
       </c>
       <c r="AA2">
-        <v>-0.07768595041322314</v>
+        <v>-0.1947363347151258</v>
       </c>
       <c r="AB2">
-        <v>0.2291932889103916</v>
+        <v>0.1273531304065603</v>
       </c>
       <c r="AC2">
-        <v>-0.3068792393236148</v>
+        <v>-0.3220270483034794</v>
       </c>
       <c r="AD2">
-        <v>5.173</v>
+        <v>4.073</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>5.173</v>
+        <v>4.073</v>
       </c>
       <c r="AG2">
-        <v>-33.497</v>
+        <v>-5.670999999999999</v>
       </c>
       <c r="AH2">
-        <v>0.008723984464460684</v>
+        <v>0.009810368207951867</v>
       </c>
       <c r="AI2">
-        <v>0.0197863396610351</v>
+        <v>0.01641127716241644</v>
       </c>
       <c r="AJ2">
-        <v>-0.06043193762143848</v>
+        <v>-0.0139876525852862</v>
       </c>
       <c r="AK2">
-        <v>-0.1503638232640401</v>
+        <v>-0.02378386086168789</v>
       </c>
       <c r="AL2">
-        <v>0.462</v>
+        <v>0.371</v>
       </c>
       <c r="AM2">
-        <v>0.369</v>
+        <v>-0.339</v>
       </c>
       <c r="AN2">
-        <v>-1.01153695737192</v>
+        <v>-0.233865411116215</v>
       </c>
       <c r="AO2">
-        <v>-32.32034632034632</v>
+        <v>-52.96495956873315</v>
       </c>
       <c r="AP2">
-        <v>6.550058662495111</v>
+        <v>0.3256201194304087</v>
       </c>
       <c r="AQ2">
-        <v>-40.46612466124662</v>
+        <v>57.9646017699115</v>
       </c>
     </row>
     <row r="3">
@@ -707,7 +689,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Arc Minerals Limited (AIM:ARCM)</t>
+          <t>Talon Metals Corp. (TSX:TLO)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -716,7 +698,7 @@
         </is>
       </c>
       <c r="K3">
-        <v>-10.2</v>
+        <v>-1.68</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -740,67 +722,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>2.85</v>
+        <v>3.88</v>
       </c>
       <c r="V3">
-        <v>0.06129032258064517</v>
+        <v>0.03052714398111723</v>
       </c>
       <c r="W3">
-        <v>-1.387755102040816</v>
+        <v>-0.01280487804878049</v>
       </c>
       <c r="X3">
-        <v>0.243779012785569</v>
+        <v>0.1273841351454899</v>
       </c>
       <c r="Y3">
-        <v>-1.631534114826385</v>
+        <v>-0.1401890131942704</v>
       </c>
       <c r="Z3">
         <v>0</v>
       </c>
       <c r="AA3">
-        <v>0.1183833116036506</v>
+        <v>-0.01669847328244275</v>
       </c>
       <c r="AB3">
-        <v>0.230342083528952</v>
+        <v>0.1273841351454899</v>
       </c>
       <c r="AC3">
-        <v>-0.1119587719253014</v>
+        <v>-0.1440826084279327</v>
       </c>
       <c r="AD3">
-        <v>4.79</v>
+        <v>0</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>4.79</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>1.94</v>
+        <v>-3.88</v>
       </c>
       <c r="AH3">
-        <v>0.09339052446870735</v>
+        <v>0</v>
       </c>
       <c r="AI3">
-        <v>0.4402573529411765</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>0.04004954582989265</v>
+        <v>-0.03148839474111346</v>
       </c>
       <c r="AK3">
-        <v>0.2415940224159402</v>
+        <v>-0.02511001812063163</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>0.027</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="AN3">
-        <v>5.286975717439294</v>
+        <v>-0</v>
+      </c>
+      <c r="AO3">
+        <v>-77.77777777777779</v>
       </c>
       <c r="AP3">
-        <v>2.141280353200883</v>
+        <v>1.874396135265701</v>
+      </c>
+      <c r="AQ3">
+        <v>3.5</v>
       </c>
     </row>
     <row r="4">
@@ -811,7 +799,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Talon Metals Corp. (TSX:TLO)</t>
+          <t>Phoenix Copper Limited (AIM:PXC)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -820,7 +808,7 @@
         </is>
       </c>
       <c r="K4">
-        <v>-1.44</v>
+        <v>-1.12</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -844,70 +832,64 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>5.44</v>
+        <v>2.75</v>
       </c>
       <c r="V4">
-        <v>0.01748071979434447</v>
+        <v>0.08136094674556214</v>
       </c>
       <c r="W4">
-        <v>-0.01512605042016807</v>
+        <v>-0.02939632545931759</v>
       </c>
       <c r="X4">
-        <v>0.2291932889103916</v>
+        <v>0.1308436339144854</v>
       </c>
       <c r="Y4">
-        <v>-0.2443193393305597</v>
+        <v>-0.160239959373803</v>
       </c>
       <c r="Z4">
         <v>0</v>
       </c>
       <c r="AA4">
-        <v>-0.0393371757925072</v>
+        <v>-0.06058519793459553</v>
       </c>
       <c r="AB4">
-        <v>0.2291932889103916</v>
+        <v>0.1267160715711764</v>
       </c>
       <c r="AC4">
-        <v>-0.2685304647028988</v>
+        <v>-0.1873012695057719</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG4">
-        <v>-5.44</v>
+        <v>-0.75</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>0.0558659217877095</v>
       </c>
       <c r="AI4">
-        <v>0</v>
+        <v>0.05076142131979695</v>
       </c>
       <c r="AJ4">
-        <v>-0.01779173207744637</v>
+        <v>-0.0226928895612708</v>
       </c>
       <c r="AK4">
-        <v>-0.04325699745547074</v>
+        <v>-0.02046384720327422</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-0.082</v>
-      </c>
-      <c r="AN4">
-        <v>-0</v>
-      </c>
-      <c r="AP4">
-        <v>2.007380073800738</v>
+        <v>-0.047</v>
       </c>
       <c r="AQ4">
-        <v>33.29268292682926</v>
+        <v>37.4468085106383</v>
       </c>
     </row>
     <row r="5">
@@ -918,7 +900,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Phoenix Copper Limited (AIM:PXC)</t>
+          <t>Alpha Exploration Ltd. (TSXV:ALEX)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -927,7 +909,7 @@
         </is>
       </c>
       <c r="K5">
-        <v>-1.8</v>
+        <v>-1.69</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -951,31 +933,31 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>9.050000000000001</v>
+        <v>0.723</v>
       </c>
       <c r="V5">
-        <v>0.2149643705463183</v>
+        <v>0.02036619718309859</v>
       </c>
       <c r="W5">
-        <v>-0.04787234042553191</v>
+        <v>-0.1713995943204868</v>
       </c>
       <c r="X5">
-        <v>0.2291932889103916</v>
+        <v>0.1273841351454899</v>
       </c>
       <c r="Y5">
-        <v>-0.2770656293359235</v>
+        <v>-0.2987837294659768</v>
       </c>
       <c r="Z5">
         <v>0</v>
       </c>
       <c r="AA5">
-        <v>-0.05792163543441225</v>
+        <v>-0.115756349741515</v>
       </c>
       <c r="AB5">
-        <v>0.2291932889103916</v>
+        <v>0.1273841351454899</v>
       </c>
       <c r="AC5">
-        <v>-0.2871149243448038</v>
+        <v>-0.2431404848870049</v>
       </c>
       <c r="AD5">
         <v>0</v>
@@ -987,7 +969,7 @@
         <v>0</v>
       </c>
       <c r="AG5">
-        <v>-9.050000000000001</v>
+        <v>-0.723</v>
       </c>
       <c r="AH5">
         <v>0</v>
@@ -996,22 +978,28 @@
         <v>0</v>
       </c>
       <c r="AJ5">
-        <v>-0.2738275340393344</v>
+        <v>-0.02078960232337464</v>
       </c>
       <c r="AK5">
-        <v>-0.3104631217838765</v>
+        <v>-0.06771565046361337</v>
       </c>
       <c r="AL5">
-        <v>0.003</v>
+        <v>0.017</v>
       </c>
       <c r="AM5">
-        <v>-0.007</v>
+        <v>0.017</v>
+      </c>
+      <c r="AN5">
+        <v>-0</v>
       </c>
       <c r="AO5">
-        <v>-340</v>
+        <v>-60.58823529411764</v>
+      </c>
+      <c r="AP5">
+        <v>0.7642706131078224</v>
       </c>
       <c r="AQ5">
-        <v>145.7142857142857</v>
+        <v>-60.58823529411764</v>
       </c>
     </row>
     <row r="6">
@@ -1022,7 +1010,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Amur Minerals Corporation (AIM:AMC)</t>
+          <t>Lefroy Exploration Limited (ASX:LEX)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1031,7 +1019,7 @@
         </is>
       </c>
       <c r="K6">
-        <v>-3.39</v>
+        <v>-2</v>
       </c>
       <c r="M6">
         <v>-0</v>
@@ -1055,67 +1043,73 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>5.31</v>
+        <v>0.294</v>
       </c>
       <c r="V6">
-        <v>0.3160714285714286</v>
+        <v>0.01283842794759825</v>
       </c>
       <c r="W6">
-        <v>-0.105607476635514</v>
+        <v>-0.1526717557251908</v>
       </c>
       <c r="X6">
-        <v>0.2291932889103916</v>
+        <v>0.1277849686862662</v>
       </c>
       <c r="Y6">
-        <v>-0.3348007655459057</v>
+        <v>-0.280456724411457</v>
       </c>
       <c r="Z6">
         <v>0</v>
       </c>
       <c r="AA6">
-        <v>-0.07768595041322314</v>
+        <v>-0.1947363347151258</v>
       </c>
       <c r="AB6">
-        <v>0.2291932889103916</v>
+        <v>0.1272907135883536</v>
       </c>
       <c r="AC6">
-        <v>-0.3068792393236148</v>
+        <v>-0.3220270483034794</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>0.157</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>0.157</v>
       </c>
       <c r="AG6">
-        <v>-5.31</v>
+        <v>-0.137</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>0.006809211952986079</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>0.0115807332005606</v>
       </c>
       <c r="AJ6">
-        <v>-0.4621409921671017</v>
+        <v>-0.006018538856916927</v>
       </c>
       <c r="AK6">
-        <v>-0.1675607447144209</v>
+        <v>-0.01032948804946091</v>
       </c>
       <c r="AL6">
-        <v>0.327</v>
+        <v>0.006</v>
       </c>
       <c r="AM6">
-        <v>0.327</v>
+        <v>-0.02</v>
+      </c>
+      <c r="AN6">
+        <v>-0.07810945273631842</v>
       </c>
       <c r="AO6">
-        <v>-7.186544342507645</v>
+        <v>-336.6666666666667</v>
+      </c>
+      <c r="AP6">
+        <v>0.0681592039800995</v>
       </c>
       <c r="AQ6">
-        <v>-7.186544342507645</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7">
@@ -1126,7 +1120,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Lefroy Exploration Limited (ASX:LEX)</t>
+          <t>Premier African Minerals Limited (AIM:PREM)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1134,26 +1128,8 @@
           <t>Metals &amp; Mining</t>
         </is>
       </c>
-      <c r="D7">
-        <v>0.38</v>
-      </c>
-      <c r="G7">
-        <v>-231.4285714285714</v>
-      </c>
-      <c r="H7">
-        <v>-231.4285714285714</v>
-      </c>
-      <c r="I7">
-        <v>-234.2857142857143</v>
-      </c>
-      <c r="J7">
-        <v>-234.2857142857143</v>
-      </c>
       <c r="K7">
-        <v>-1.64</v>
-      </c>
-      <c r="L7">
-        <v>-234.2857142857143</v>
+        <v>-8</v>
       </c>
       <c r="M7">
         <v>-0</v>
@@ -1177,73 +1153,73 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>2.93</v>
+        <v>0.231</v>
       </c>
       <c r="V7">
-        <v>0.1097378277153558</v>
+        <v>0.003063660477453581</v>
       </c>
       <c r="W7">
-        <v>-0.1490909090909091</v>
+        <v>-0.217983651226158</v>
       </c>
       <c r="X7">
-        <v>0.2302698289909256</v>
+        <v>0.1275361145052037</v>
       </c>
       <c r="Y7">
-        <v>-0.3793607380818347</v>
+        <v>-0.3455197657313618</v>
       </c>
       <c r="Z7">
-        <v>0.0008244994110718492</v>
+        <v>0</v>
       </c>
       <c r="AA7">
-        <v>-0.1931684334511189</v>
+        <v>-0.242503748125937</v>
       </c>
       <c r="AB7">
-        <v>0.2293074316854285</v>
+        <v>0.1273531304065603</v>
       </c>
       <c r="AC7">
-        <v>-0.4224758651365474</v>
+        <v>-0.3698568785324974</v>
       </c>
       <c r="AD7">
-        <v>0.203</v>
+        <v>0.196</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>0.203</v>
+        <v>0.196</v>
       </c>
       <c r="AG7">
-        <v>-2.727</v>
+        <v>-0.035</v>
       </c>
       <c r="AH7">
-        <v>0.0075456268817604</v>
+        <v>0.00259272977406212</v>
       </c>
       <c r="AI7">
-        <v>0.01525971585356687</v>
+        <v>0.01543793320730939</v>
       </c>
       <c r="AJ7">
-        <v>-0.1137529720936053</v>
+        <v>-0.0004644065547668016</v>
       </c>
       <c r="AK7">
-        <v>-0.2628940518654199</v>
+        <v>-0.002807862013638187</v>
       </c>
       <c r="AL7">
-        <v>0.003</v>
+        <v>0.321</v>
       </c>
       <c r="AM7">
-        <v>0.002</v>
+        <v>0.321</v>
       </c>
       <c r="AN7">
-        <v>-0.1253086419753086</v>
+        <v>-0.03116057233704293</v>
       </c>
       <c r="AO7">
-        <v>-546.6666666666666</v>
+        <v>-20.15576323987539</v>
       </c>
       <c r="AP7">
-        <v>1.683333333333333</v>
+        <v>0.005564387917329094</v>
       </c>
       <c r="AQ7">
-        <v>-819.9999999999999</v>
+        <v>-20.15576323987539</v>
       </c>
     </row>
     <row r="8">
@@ -1254,7 +1230,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Premier African Minerals Limited (AIM:PREM)</t>
+          <t>Empire Metals Limited (AIM:EEE)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1263,7 +1239,7 @@
         </is>
       </c>
       <c r="K8">
-        <v>-6.08</v>
+        <v>-1.99</v>
       </c>
       <c r="M8">
         <v>-0</v>
@@ -1287,67 +1263,70 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>10.2</v>
+        <v>1.79</v>
       </c>
       <c r="V8">
-        <v>0.07402031930333816</v>
+        <v>0.02644017725258493</v>
       </c>
       <c r="W8">
-        <v>-0.2356589147286822</v>
+        <v>-0.3119122257053292</v>
       </c>
       <c r="X8">
-        <v>0.2293782450339607</v>
+        <v>0.1273841351454899</v>
       </c>
       <c r="Y8">
-        <v>-0.4650371597626428</v>
+        <v>-0.4392963608508191</v>
       </c>
       <c r="Z8">
         <v>0</v>
       </c>
       <c r="AA8">
-        <v>-0.2578128142219362</v>
+        <v>-0.512893982808023</v>
       </c>
       <c r="AB8">
-        <v>0.2293058684170567</v>
+        <v>0.1273841351454899</v>
       </c>
       <c r="AC8">
-        <v>-0.4871186826389929</v>
+        <v>-0.640278117953513</v>
       </c>
       <c r="AD8">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="AG8">
-        <v>-10.02</v>
+        <v>-1.79</v>
       </c>
       <c r="AH8">
-        <v>0.001304536889404261</v>
+        <v>0</v>
       </c>
       <c r="AI8">
-        <v>0.007352941176470588</v>
+        <v>0</v>
       </c>
       <c r="AJ8">
-        <v>-0.07841602754734699</v>
+        <v>-0.02715824609315734</v>
       </c>
       <c r="AK8">
-        <v>-0.7016806722689075</v>
+        <v>-0.3784355179704018</v>
       </c>
       <c r="AL8">
-        <v>0.129</v>
+        <v>0</v>
       </c>
       <c r="AM8">
-        <v>0.129</v>
-      </c>
-      <c r="AO8">
-        <v>-49.68992248062015</v>
+        <v>-0.01</v>
+      </c>
+      <c r="AN8">
+        <v>-0</v>
+      </c>
+      <c r="AP8">
+        <v>1.091463414634146</v>
       </c>
       <c r="AQ8">
-        <v>-49.68992248062015</v>
+        <v>179</v>
       </c>
     </row>
     <row r="9">
@@ -1358,7 +1337,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Empire Metals Limited (AIM:EEE)</t>
+          <t>Arc Minerals Limited (AIM:ARCM)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1367,7 +1346,7 @@
         </is>
       </c>
       <c r="K9">
-        <v>-2.31</v>
+        <v>-3.77</v>
       </c>
       <c r="M9">
         <v>-0</v>
@@ -1391,55 +1370,55 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>2.89</v>
+        <v>0.076</v>
       </c>
       <c r="V9">
-        <v>0.4319880418535127</v>
+        <v>0.001560574948665298</v>
       </c>
       <c r="W9">
-        <v>-0.330945558739255</v>
+        <v>-0.6032</v>
       </c>
       <c r="X9">
-        <v>0.2291932889103916</v>
+        <v>0.1294490367926596</v>
       </c>
       <c r="Y9">
-        <v>-0.5601388476496466</v>
+        <v>-0.7326490367926595</v>
       </c>
       <c r="Z9">
         <v>0</v>
       </c>
       <c r="AA9">
-        <v>-0.5807560137457044</v>
+        <v>-0.5470085470085471</v>
       </c>
       <c r="AB9">
-        <v>0.2291932889103916</v>
+        <v>0.1269161028145505</v>
       </c>
       <c r="AC9">
-        <v>-0.809949302656096</v>
+        <v>-0.6739246498230975</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG9">
-        <v>-2.89</v>
+        <v>1.644</v>
       </c>
       <c r="AH9">
-        <v>0</v>
+        <v>0.03411344704482348</v>
       </c>
       <c r="AI9">
-        <v>0</v>
+        <v>0.2769726247987118</v>
       </c>
       <c r="AJ9">
-        <v>-0.7605263157894737</v>
+        <v>0.03265533132051485</v>
       </c>
       <c r="AK9">
-        <v>-0.8280802292263612</v>
+        <v>0.2680143462667101</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1448,10 +1427,10 @@
         <v>0</v>
       </c>
       <c r="AN9">
-        <v>-0</v>
+        <v>-0.3856502242152466</v>
       </c>
       <c r="AP9">
-        <v>1.710059171597633</v>
+        <v>-0.368609865470852</v>
       </c>
     </row>
   </sheetData>
